--- a/output_boron/boron_Intermediate_chalk_2017.xlsx
+++ b/output_boron/boron_Intermediate_chalk_2017.xlsx
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">10.1073/pnas.1702143114</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/boron_isotopes_chalk_2017.xlsx</t>
+    <t xml:space="preserve">boron_isotopes_chalk_2017_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>
@@ -1559,13 +1559,13 @@
     <t xml:space="preserve">ODP 999_A_4_7_22_24</t>
   </si>
   <si>
-    <t xml:space="preserve">ODP 999_A_4_7_32.8883769999998_34.8883769999998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ODP 999_A_4_7_41.6941029999998_43.6941029999998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ODP 999_A_4_7_51.6954790000001_53.6954790000001</t>
+    <t xml:space="preserve">ODP 999_A_4_7_32.888376999999849_34.888376999999849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODP 999_A_4_7_41.694102999999785_43.694102999999785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODP 999_A_4_7_51.695479000000091_53.695479000000091</t>
   </si>
   <si>
     <t xml:space="preserve">ODP 999_A_4_7_60_62</t>
@@ -1580,25 +1580,25 @@
     <t xml:space="preserve">ODP 999_A_5_1_17_19</t>
   </si>
   <si>
-    <t xml:space="preserve">ODP 999_A_5_1_37.5173090000004_39.5173090000004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ODP 999_A_5_1_48.3991950000003_50.3991950000003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ODP 999_A_5_1_59.2812659999999_61.2812659999999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ODP 999_A_5_1_70.1630350000001_72.1630350000001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ODP 999_A_5_1_80.8929320000004_82.8929320000004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ODP 999_A_5_1_90.3610010000001_92.3610010000001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ODP 999_A_5_1_98.80171_100.80171</t>
+    <t xml:space="preserve">ODP 999_A_5_1_37.517309000000353_39.517309000000353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODP 999_A_5_1_48.399195000000304_50.399195000000304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODP 999_A_5_1_59.281265999999931_61.281265999999931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODP 999_A_5_1_70.16303500000015_72.16303500000015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODP 999_A_5_1_80.892932000000371_82.892932000000371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODP 999_A_5_1_90.361001000000073_92.361001000000073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODP 999_A_5_1_98.801709999999986_100.80170999999999</t>
   </si>
   <si>
     <t xml:space="preserve">ODP 999_A_5_1_108_110</t>
@@ -1616,7 +1616,7 @@
     <t xml:space="preserve">ODP 999_A_5_1_148_150</t>
   </si>
   <si>
-    <t xml:space="preserve">ODP 999_A_5_2_7.88640199999969_9.88640199999969</t>
+    <t xml:space="preserve">ODP 999_A_5_2_7.8864019999996913_9.8864019999996913</t>
   </si>
   <si>
     <t xml:space="preserve">ODP 999_A_5_2_17_19</t>
@@ -1625,7 +1625,7 @@
     <t xml:space="preserve">ODP 999_A_5_2_23_25</t>
   </si>
   <si>
-    <t xml:space="preserve">ODP 999_A_5_2_33.2083490000002_35.2083490000002</t>
+    <t xml:space="preserve">ODP 999_A_5_2_33.208349000000169_35.208349000000169</t>
   </si>
   <si>
     <t xml:space="preserve">ODP 999_A_5_2_39_41</t>
@@ -1634,10 +1634,10 @@
     <t xml:space="preserve">ODP 999_A_5_2_48_50</t>
   </si>
   <si>
-    <t xml:space="preserve">ODP 999_A_5_2_58.5305750000003_60.5305750000003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ODP 999_A_5_2_66.9712349999997_68.9712349999997</t>
+    <t xml:space="preserve">ODP 999_A_5_2_58.530575000000283_60.530575000000283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODP 999_A_5_2_66.971234999999695_68.971234999999695</t>
   </si>
   <si>
     <t xml:space="preserve">ODP 999_A_5_2_73_75</t>
@@ -1646,25 +1646,25 @@
     <t xml:space="preserve">ODP 999_A_5_2_93_95</t>
   </si>
   <si>
-    <t xml:space="preserve">ODP 999_A_5_2_120.225904_122.225904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ODP 999_A_5_2_130.456421_132.456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ODP 999_A_5_2_140.686983_142.686983</t>
+    <t xml:space="preserve">ODP 999_A_5_2_120.22590400000007_122.22590400000007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODP 999_A_5_2_130.45642100000018_132.45642100000018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODP 999_A_5_2_140.68698299999974_142.68698299999974</t>
   </si>
   <si>
     <t xml:space="preserve">ODP 999_A_5_3_2_4</t>
   </si>
   <si>
-    <t xml:space="preserve">ODP 999_A_5_3_10.1112679999999_12.1112679999999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ODP 999_A_5_3_18.570803_20.570803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ODP 999_A_5_3_27.0297110000001_29.0297110000001</t>
+    <t xml:space="preserve">ODP 999_A_5_3_10.111267999999939_12.111267999999939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODP 999_A_5_3_18.570803000000012_20.570803000000012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODP 999_A_5_3_27.029711000000077_29.029711000000077</t>
   </si>
   <si>
     <t xml:space="preserve">ODP 999_A_5_3_37_39</t>
@@ -1676,10 +1676,10 @@
     <t xml:space="preserve">ODP 999_A_5_3_67_69</t>
   </si>
   <si>
-    <t xml:space="preserve">ODP 999_A_5_3_77.7851810000001_79.7851810000001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ODP 999_A_5_3_94.703501_96.703501</t>
+    <t xml:space="preserve">ODP 999_A_5_3_77.78518100000008_79.78518100000008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODP 999_A_5_3_94.703500999999989_96.703500999999989</t>
   </si>
   <si>
     <t xml:space="preserve">ODP 999_A_5_3_102_104</t>
@@ -1688,10 +1688,10 @@
     <t xml:space="preserve">ODP 999_A_5_3_110_112</t>
   </si>
   <si>
-    <t xml:space="preserve">ODP 999_A_5_3_128.540584_130.540584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ODP 999_A_5_3_136.999882_138.999882</t>
+    <t xml:space="preserve">ODP 999_A_5_3_128.54058400000022_130.54058400000022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODP 999_A_5_3_136.99988199999987_138.99988199999987</t>
   </si>
   <si>
     <t xml:space="preserve">ODP 999_A_5_3_147_149</t>
@@ -1700,7 +1700,7 @@
     <t xml:space="preserve">ODP 999_A_5_4_6_8</t>
   </si>
   <si>
-    <t xml:space="preserve">ODP 999_A_5_4_12.4591639999998_14.4591639999998</t>
+    <t xml:space="preserve">ODP 999_A_5_4_12.459163999999788_14.459163999999788</t>
   </si>
   <si>
     <t xml:space="preserve">ODP 999_A_5_4_21_23</t>
@@ -1714,7 +1714,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1774,12 +1774,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1893,7 +1887,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1975,7 +1969,6 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2582,7 +2575,7 @@
       <c r="B5" t="s">
         <v>241</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" t="s">
         <v>242</v>
       </c>
       <c r="D5" t="s">
@@ -2601,7 +2594,7 @@
         <v>0.003911025047</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002</v>
+        <v>0.000035</v>
       </c>
       <c r="J5" t="e">
         <v>#N/A</v>
@@ -2659,7 +2652,7 @@
       <c r="B6" t="s">
         <v>241</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" t="s">
         <v>242</v>
       </c>
       <c r="D6" t="s">
@@ -2678,7 +2671,7 @@
         <v>0.00463</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002</v>
+        <v>0.000035</v>
       </c>
       <c r="J6" t="e">
         <v>#N/A</v>
@@ -2736,7 +2729,7 @@
       <c r="B7" t="s">
         <v>241</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" t="s">
         <v>242</v>
       </c>
       <c r="D7" t="s">
@@ -2755,7 +2748,7 @@
         <v>0.00502</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002</v>
+        <v>0.000035</v>
       </c>
       <c r="J7" t="e">
         <v>#N/A</v>
@@ -2813,7 +2806,7 @@
       <c r="B8" t="s">
         <v>241</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" t="s">
         <v>242</v>
       </c>
       <c r="D8" t="s">
@@ -2832,7 +2825,7 @@
         <v>0.00782</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002</v>
+        <v>0.000035</v>
       </c>
       <c r="J8" t="e">
         <v>#N/A</v>
@@ -2890,7 +2883,7 @@
       <c r="B9" t="s">
         <v>241</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" t="s">
         <v>242</v>
       </c>
       <c r="D9" t="s">
@@ -2909,7 +2902,7 @@
         <v>0.00782</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002</v>
+        <v>0.000035</v>
       </c>
       <c r="J9" t="e">
         <v>#N/A</v>
@@ -2967,7 +2960,7 @@
       <c r="B10" t="s">
         <v>241</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" t="s">
         <v>242</v>
       </c>
       <c r="D10" t="s">
@@ -2986,7 +2979,7 @@
         <v>0.00949</v>
       </c>
       <c r="I10" t="n">
-        <v>0.002</v>
+        <v>0.000035</v>
       </c>
       <c r="J10" t="e">
         <v>#N/A</v>
@@ -3044,7 +3037,7 @@
       <c r="B11" t="s">
         <v>241</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" t="s">
         <v>242</v>
       </c>
       <c r="D11" t="s">
@@ -3063,7 +3056,7 @@
         <v>0.01032</v>
       </c>
       <c r="I11" t="n">
-        <v>0.002</v>
+        <v>0.000035</v>
       </c>
       <c r="J11" t="e">
         <v>#N/A</v>
@@ -3121,7 +3114,7 @@
       <c r="B12" t="s">
         <v>241</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" t="s">
         <v>242</v>
       </c>
       <c r="D12" t="s">
@@ -3140,7 +3133,7 @@
         <v>0.01165</v>
       </c>
       <c r="I12" t="n">
-        <v>0.002</v>
+        <v>0.000035</v>
       </c>
       <c r="J12" t="e">
         <v>#N/A</v>
@@ -3198,7 +3191,7 @@
       <c r="B13" t="s">
         <v>241</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" t="s">
         <v>242</v>
       </c>
       <c r="D13" t="s">
@@ -3217,7 +3210,7 @@
         <v>0.01401</v>
       </c>
       <c r="I13" t="n">
-        <v>0.002</v>
+        <v>0.000035</v>
       </c>
       <c r="J13" t="e">
         <v>#N/A</v>
@@ -3275,7 +3268,7 @@
       <c r="B14" t="s">
         <v>241</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C14" t="s">
         <v>242</v>
       </c>
       <c r="D14" t="s">
@@ -3294,7 +3287,7 @@
         <v>0.01507</v>
       </c>
       <c r="I14" t="n">
-        <v>0.002</v>
+        <v>0.000035</v>
       </c>
       <c r="J14" t="e">
         <v>#N/A</v>
@@ -3352,7 +3345,7 @@
       <c r="B15" t="s">
         <v>241</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="C15" t="s">
         <v>242</v>
       </c>
       <c r="D15" t="s">
@@ -3371,7 +3364,7 @@
         <v>0.01507</v>
       </c>
       <c r="I15" t="n">
-        <v>0.002</v>
+        <v>0.000035</v>
       </c>
       <c r="J15" t="e">
         <v>#N/A</v>
@@ -3429,7 +3422,7 @@
       <c r="B16" t="s">
         <v>241</v>
       </c>
-      <c r="C16" s="29" t="s">
+      <c r="C16" t="s">
         <v>242</v>
       </c>
       <c r="D16" t="s">
@@ -3448,7 +3441,7 @@
         <v>0.01726</v>
       </c>
       <c r="I16" t="n">
-        <v>0.002</v>
+        <v>0.000035</v>
       </c>
       <c r="J16" t="e">
         <v>#N/A</v>
@@ -3506,7 +3499,7 @@
       <c r="B17" t="s">
         <v>241</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C17" t="s">
         <v>242</v>
       </c>
       <c r="D17" t="s">
@@ -3525,7 +3518,7 @@
         <v>0.01919</v>
       </c>
       <c r="I17" t="n">
-        <v>0.002</v>
+        <v>0.000035</v>
       </c>
       <c r="J17" t="e">
         <v>#N/A</v>
@@ -3583,7 +3576,7 @@
       <c r="B18" t="s">
         <v>241</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C18" t="s">
         <v>242</v>
       </c>
       <c r="D18" t="s">
@@ -3602,7 +3595,7 @@
         <v>0.02112</v>
       </c>
       <c r="I18" t="n">
-        <v>0.002</v>
+        <v>0.000035</v>
       </c>
       <c r="J18" t="e">
         <v>#N/A</v>
@@ -3660,7 +3653,7 @@
       <c r="B19" t="s">
         <v>241</v>
       </c>
-      <c r="C19" s="29" t="s">
+      <c r="C19" t="s">
         <v>242</v>
       </c>
       <c r="D19" t="s">
@@ -3679,7 +3672,7 @@
         <v>0.02261</v>
       </c>
       <c r="I19" t="n">
-        <v>0.002</v>
+        <v>0.000035</v>
       </c>
       <c r="J19" t="e">
         <v>#N/A</v>
@@ -3737,7 +3730,7 @@
       <c r="B20" t="s">
         <v>241</v>
       </c>
-      <c r="C20" s="29" t="s">
+      <c r="C20" t="s">
         <v>242</v>
       </c>
       <c r="D20" t="s">
@@ -3756,7 +3749,7 @@
         <v>0.02438</v>
       </c>
       <c r="I20" t="n">
-        <v>0.002</v>
+        <v>0.000035</v>
       </c>
       <c r="J20" t="e">
         <v>#N/A</v>
@@ -3814,7 +3807,7 @@
       <c r="B21" t="s">
         <v>241</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" t="s">
         <v>242</v>
       </c>
       <c r="D21" t="s">
@@ -3833,7 +3826,7 @@
         <v>0.02551</v>
       </c>
       <c r="I21" t="n">
-        <v>0.002</v>
+        <v>0.000035</v>
       </c>
       <c r="J21" t="e">
         <v>#N/A</v>
@@ -3891,7 +3884,7 @@
       <c r="B22" t="s">
         <v>241</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="C22" t="s">
         <v>242</v>
       </c>
       <c r="D22" t="s">
@@ -3910,7 +3903,7 @@
         <v>0.02551</v>
       </c>
       <c r="I22" t="n">
-        <v>0.002</v>
+        <v>0.000035</v>
       </c>
       <c r="J22" t="e">
         <v>#N/A</v>
@@ -3968,7 +3961,7 @@
       <c r="B23" t="s">
         <v>241</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" t="s">
         <v>242</v>
       </c>
       <c r="D23" t="s">
@@ -3987,7 +3980,7 @@
         <v>0.03582</v>
       </c>
       <c r="I23" t="n">
-        <v>0.002</v>
+        <v>0.000035</v>
       </c>
       <c r="J23" t="e">
         <v>#N/A</v>
@@ -4045,7 +4038,7 @@
       <c r="B24" t="s">
         <v>241</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="C24" t="s">
         <v>242</v>
       </c>
       <c r="D24" t="s">
@@ -4064,7 +4057,7 @@
         <v>0.04661</v>
       </c>
       <c r="I24" t="n">
-        <v>0.002</v>
+        <v>0.000035</v>
       </c>
       <c r="J24" t="e">
         <v>#N/A</v>
@@ -4122,7 +4115,7 @@
       <c r="B25" t="s">
         <v>241</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" t="s">
         <v>242</v>
       </c>
       <c r="D25" t="s">
@@ -4141,7 +4134,7 @@
         <v>0.05214</v>
       </c>
       <c r="I25" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J25" t="e">
         <v>#N/A</v>
@@ -4199,7 +4192,7 @@
       <c r="B26" t="s">
         <v>241</v>
       </c>
-      <c r="C26" s="29" t="s">
+      <c r="C26" t="s">
         <v>242</v>
       </c>
       <c r="D26" t="s">
@@ -4218,7 +4211,7 @@
         <v>0.06128</v>
       </c>
       <c r="I26" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J26" t="e">
         <v>#N/A</v>
@@ -4276,7 +4269,7 @@
       <c r="B27" t="s">
         <v>241</v>
       </c>
-      <c r="C27" s="29" t="s">
+      <c r="C27" t="s">
         <v>242</v>
       </c>
       <c r="D27" t="s">
@@ -4295,7 +4288,7 @@
         <v>0.0773</v>
       </c>
       <c r="I27" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J27" t="e">
         <v>#N/A</v>
@@ -4353,7 +4346,7 @@
       <c r="B28" t="s">
         <v>241</v>
       </c>
-      <c r="C28" s="29" t="s">
+      <c r="C28" t="s">
         <v>242</v>
       </c>
       <c r="D28" t="s">
@@ -4372,7 +4365,7 @@
         <v>0.08433</v>
       </c>
       <c r="I28" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J28" t="e">
         <v>#N/A</v>
@@ -4430,7 +4423,7 @@
       <c r="B29" t="s">
         <v>241</v>
       </c>
-      <c r="C29" s="29" t="s">
+      <c r="C29" t="s">
         <v>242</v>
       </c>
       <c r="D29" t="s">
@@ -4449,7 +4442,7 @@
         <v>0.08911</v>
       </c>
       <c r="I29" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J29" t="e">
         <v>#N/A</v>
@@ -4507,7 +4500,7 @@
       <c r="B30" t="s">
         <v>241</v>
       </c>
-      <c r="C30" s="29" t="s">
+      <c r="C30" t="s">
         <v>242</v>
       </c>
       <c r="D30" t="s">
@@ -4526,7 +4519,7 @@
         <v>0.10036</v>
       </c>
       <c r="I30" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J30" t="e">
         <v>#N/A</v>
@@ -4584,7 +4577,7 @@
       <c r="B31" t="s">
         <v>241</v>
       </c>
-      <c r="C31" s="29" t="s">
+      <c r="C31" t="s">
         <v>242</v>
       </c>
       <c r="D31" t="s">
@@ -4603,7 +4596,7 @@
         <v>0.10612</v>
       </c>
       <c r="I31" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J31" t="e">
         <v>#N/A</v>
@@ -4661,7 +4654,7 @@
       <c r="B32" t="s">
         <v>241</v>
       </c>
-      <c r="C32" s="29" t="s">
+      <c r="C32" t="s">
         <v>242</v>
       </c>
       <c r="D32" t="s">
@@ -4680,7 +4673,7 @@
         <v>0.11132</v>
       </c>
       <c r="I32" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J32" t="e">
         <v>#N/A</v>
@@ -4738,7 +4731,7 @@
       <c r="B33" t="s">
         <v>241</v>
       </c>
-      <c r="C33" s="29" t="s">
+      <c r="C33" t="s">
         <v>242</v>
       </c>
       <c r="D33" t="s">
@@ -4757,7 +4750,7 @@
         <v>0.11682</v>
       </c>
       <c r="I33" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J33" t="e">
         <v>#N/A</v>
@@ -4815,7 +4808,7 @@
       <c r="B34" t="s">
         <v>241</v>
       </c>
-      <c r="C34" s="29" t="s">
+      <c r="C34" t="s">
         <v>242</v>
       </c>
       <c r="D34" t="s">
@@ -4834,7 +4827,7 @@
         <v>0.11881</v>
       </c>
       <c r="I34" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J34" t="e">
         <v>#N/A</v>
@@ -4892,7 +4885,7 @@
       <c r="B35" t="s">
         <v>241</v>
       </c>
-      <c r="C35" s="29" t="s">
+      <c r="C35" t="s">
         <v>242</v>
       </c>
       <c r="D35" t="s">
@@ -4911,7 +4904,7 @@
         <v>0.11906</v>
       </c>
       <c r="I35" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J35" t="e">
         <v>#N/A</v>
@@ -4969,7 +4962,7 @@
       <c r="B36" t="s">
         <v>241</v>
       </c>
-      <c r="C36" s="29" t="s">
+      <c r="C36" t="s">
         <v>242</v>
       </c>
       <c r="D36" t="s">
@@ -4988,7 +4981,7 @@
         <v>0.12179</v>
       </c>
       <c r="I36" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J36" t="e">
         <v>#N/A</v>
@@ -5046,7 +5039,7 @@
       <c r="B37" t="s">
         <v>241</v>
       </c>
-      <c r="C37" s="29" t="s">
+      <c r="C37" t="s">
         <v>242</v>
       </c>
       <c r="D37" t="s">
@@ -5065,7 +5058,7 @@
         <v>0.12377</v>
       </c>
       <c r="I37" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J37" t="e">
         <v>#N/A</v>
@@ -5123,7 +5116,7 @@
       <c r="B38" t="s">
         <v>241</v>
       </c>
-      <c r="C38" s="29" t="s">
+      <c r="C38" t="s">
         <v>242</v>
       </c>
       <c r="D38" t="s">
@@ -5142,7 +5135,7 @@
         <v>0.12437</v>
       </c>
       <c r="I38" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J38" t="e">
         <v>#N/A</v>
@@ -5200,7 +5193,7 @@
       <c r="B39" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="29" t="s">
+      <c r="C39" t="s">
         <v>242</v>
       </c>
       <c r="D39" t="s">
@@ -5219,7 +5212,7 @@
         <v>0.12748</v>
       </c>
       <c r="I39" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J39" t="e">
         <v>#N/A</v>
@@ -5277,7 +5270,7 @@
       <c r="B40" t="s">
         <v>241</v>
       </c>
-      <c r="C40" s="29" t="s">
+      <c r="C40" t="s">
         <v>242</v>
       </c>
       <c r="D40" t="s">
@@ -5296,7 +5289,7 @@
         <v>0.13086</v>
       </c>
       <c r="I40" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J40" t="e">
         <v>#N/A</v>
@@ -5354,7 +5347,7 @@
       <c r="B41" t="s">
         <v>241</v>
       </c>
-      <c r="C41" s="29" t="s">
+      <c r="C41" t="s">
         <v>242</v>
       </c>
       <c r="D41" t="s">
@@ -5373,7 +5366,7 @@
         <v>0.13191</v>
       </c>
       <c r="I41" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J41" t="e">
         <v>#N/A</v>
@@ -5431,7 +5424,7 @@
       <c r="B42" t="s">
         <v>241</v>
       </c>
-      <c r="C42" s="29" t="s">
+      <c r="C42" t="s">
         <v>242</v>
       </c>
       <c r="D42" t="s">
@@ -5450,7 +5443,7 @@
         <v>0.13322</v>
       </c>
       <c r="I42" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J42" t="e">
         <v>#N/A</v>
@@ -5508,7 +5501,7 @@
       <c r="B43" t="s">
         <v>241</v>
       </c>
-      <c r="C43" s="29" t="s">
+      <c r="C43" t="s">
         <v>242</v>
       </c>
       <c r="D43" t="s">
@@ -5527,7 +5520,7 @@
         <v>0.134</v>
       </c>
       <c r="I43" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J43" t="e">
         <v>#N/A</v>
@@ -5585,7 +5578,7 @@
       <c r="B44" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="29" t="s">
+      <c r="C44" t="s">
         <v>242</v>
       </c>
       <c r="D44" t="s">
@@ -5604,7 +5597,7 @@
         <v>0.13557</v>
       </c>
       <c r="I44" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J44" t="e">
         <v>#N/A</v>
@@ -5662,7 +5655,7 @@
       <c r="B45" t="s">
         <v>241</v>
       </c>
-      <c r="C45" s="29" t="s">
+      <c r="C45" t="s">
         <v>242</v>
       </c>
       <c r="D45" t="s">
@@ -5681,7 +5674,7 @@
         <v>0.13897</v>
       </c>
       <c r="I45" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J45" t="e">
         <v>#N/A</v>
@@ -5739,7 +5732,7 @@
       <c r="B46" t="s">
         <v>241</v>
       </c>
-      <c r="C46" s="29" t="s">
+      <c r="C46" t="s">
         <v>242</v>
       </c>
       <c r="D46" t="s">
@@ -5758,7 +5751,7 @@
         <v>0.14669</v>
       </c>
       <c r="I46" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J46" t="e">
         <v>#N/A</v>
@@ -5816,7 +5809,7 @@
       <c r="B47" t="s">
         <v>241</v>
       </c>
-      <c r="C47" s="29" t="s">
+      <c r="C47" t="s">
         <v>242</v>
       </c>
       <c r="D47" t="s">
@@ -5835,7 +5828,7 @@
         <v>0.15004</v>
       </c>
       <c r="I47" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J47" t="e">
         <v>#N/A</v>
@@ -5893,7 +5886,7 @@
       <c r="B48" t="s">
         <v>241</v>
       </c>
-      <c r="C48" s="29" t="s">
+      <c r="C48" t="s">
         <v>242</v>
       </c>
       <c r="D48" t="s">
@@ -5912,7 +5905,7 @@
         <v>0.16976</v>
       </c>
       <c r="I48" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J48" t="e">
         <v>#N/A</v>
@@ -5970,7 +5963,7 @@
       <c r="B49" t="s">
         <v>241</v>
       </c>
-      <c r="C49" s="29" t="s">
+      <c r="C49" t="s">
         <v>242</v>
       </c>
       <c r="D49" t="s">
@@ -5989,7 +5982,7 @@
         <v>0.17994</v>
       </c>
       <c r="I49" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J49" t="e">
         <v>#N/A</v>
@@ -6047,7 +6040,7 @@
       <c r="B50" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="29" t="s">
+      <c r="C50" t="s">
         <v>242</v>
       </c>
       <c r="D50" t="s">
@@ -6066,7 +6059,7 @@
         <v>0.18437</v>
       </c>
       <c r="I50" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J50" t="e">
         <v>#N/A</v>
@@ -6124,7 +6117,7 @@
       <c r="B51" t="s">
         <v>241</v>
       </c>
-      <c r="C51" s="29" t="s">
+      <c r="C51" t="s">
         <v>242</v>
       </c>
       <c r="D51" t="s">
@@ -6143,7 +6136,7 @@
         <v>0.19001</v>
       </c>
       <c r="I51" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J51" t="e">
         <v>#N/A</v>
@@ -6201,7 +6194,7 @@
       <c r="B52" t="s">
         <v>241</v>
       </c>
-      <c r="C52" s="29" t="s">
+      <c r="C52" t="s">
         <v>242</v>
       </c>
       <c r="D52" t="s">
@@ -6220,7 +6213,7 @@
         <v>0.19168</v>
       </c>
       <c r="I52" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J52" t="e">
         <v>#N/A</v>
@@ -6278,7 +6271,7 @@
       <c r="B53" t="s">
         <v>241</v>
       </c>
-      <c r="C53" s="29" t="s">
+      <c r="C53" t="s">
         <v>242</v>
       </c>
       <c r="D53" t="s">
@@ -6297,7 +6290,7 @@
         <v>0.19807</v>
       </c>
       <c r="I53" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J53" t="e">
         <v>#N/A</v>
@@ -6355,7 +6348,7 @@
       <c r="B54" t="s">
         <v>241</v>
       </c>
-      <c r="C54" s="29" t="s">
+      <c r="C54" t="s">
         <v>242</v>
       </c>
       <c r="D54" t="s">
@@ -6374,7 +6367,7 @@
         <v>0.21157</v>
       </c>
       <c r="I54" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J54" t="e">
         <v>#N/A</v>
@@ -6432,7 +6425,7 @@
       <c r="B55" t="s">
         <v>241</v>
       </c>
-      <c r="C55" s="29" t="s">
+      <c r="C55" t="s">
         <v>242</v>
       </c>
       <c r="D55" t="s">
@@ -6451,7 +6444,7 @@
         <v>0.22044</v>
       </c>
       <c r="I55" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J55" t="e">
         <v>#N/A</v>
@@ -6509,7 +6502,7 @@
       <c r="B56" t="s">
         <v>241</v>
       </c>
-      <c r="C56" s="29" t="s">
+      <c r="C56" t="s">
         <v>242</v>
       </c>
       <c r="D56" t="s">
@@ -6528,7 +6521,7 @@
         <v>0.22366</v>
       </c>
       <c r="I56" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J56" t="e">
         <v>#N/A</v>
@@ -6586,7 +6579,7 @@
       <c r="B57" t="s">
         <v>241</v>
       </c>
-      <c r="C57" s="29" t="s">
+      <c r="C57" t="s">
         <v>242</v>
       </c>
       <c r="D57" t="s">
@@ -6605,7 +6598,7 @@
         <v>0.2271</v>
       </c>
       <c r="I57" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J57" t="e">
         <v>#N/A</v>
@@ -6663,7 +6656,7 @@
       <c r="B58" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="29" t="s">
+      <c r="C58" t="s">
         <v>242</v>
       </c>
       <c r="D58" t="s">
@@ -6682,7 +6675,7 @@
         <v>0.23576</v>
       </c>
       <c r="I58" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J58" t="e">
         <v>#N/A</v>
@@ -6740,7 +6733,7 @@
       <c r="B59" t="s">
         <v>241</v>
       </c>
-      <c r="C59" s="29" t="s">
+      <c r="C59" t="s">
         <v>242</v>
       </c>
       <c r="D59" t="s">
@@ -6759,7 +6752,7 @@
         <v>0.23948</v>
       </c>
       <c r="I59" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J59" t="e">
         <v>#N/A</v>
@@ -6817,7 +6810,7 @@
       <c r="B60" t="s">
         <v>241</v>
       </c>
-      <c r="C60" s="29" t="s">
+      <c r="C60" t="s">
         <v>242</v>
       </c>
       <c r="D60" t="s">
@@ -6836,7 +6829,7 @@
         <v>0.2429</v>
       </c>
       <c r="I60" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J60" t="e">
         <v>#N/A</v>
@@ -6894,7 +6887,7 @@
       <c r="B61" t="s">
         <v>241</v>
       </c>
-      <c r="C61" s="29" t="s">
+      <c r="C61" t="s">
         <v>242</v>
       </c>
       <c r="D61" t="s">
@@ -6913,7 +6906,7 @@
         <v>0.24718</v>
       </c>
       <c r="I61" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J61" t="e">
         <v>#N/A</v>
@@ -6971,7 +6964,7 @@
       <c r="B62" t="s">
         <v>241</v>
       </c>
-      <c r="C62" s="29" t="s">
+      <c r="C62" t="s">
         <v>242</v>
       </c>
       <c r="D62" t="s">
@@ -6990,7 +6983,7 @@
         <v>0.25007</v>
       </c>
       <c r="I62" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J62" t="e">
         <v>#N/A</v>
@@ -7048,7 +7041,7 @@
       <c r="B63" t="s">
         <v>241</v>
       </c>
-      <c r="C63" s="29" t="s">
+      <c r="C63" t="s">
         <v>242</v>
       </c>
       <c r="D63" t="s">
@@ -7067,7 +7060,7 @@
         <v>0.25784</v>
       </c>
       <c r="I63" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="J63" t="e">
         <v>#N/A</v>
@@ -7125,7 +7118,7 @@
       <c r="B64" t="s">
         <v>241</v>
       </c>
-      <c r="C64" s="29" t="s">
+      <c r="C64" t="s">
         <v>242</v>
       </c>
       <c r="D64" t="s">
@@ -7144,7 +7137,7 @@
         <v>1.08726</v>
       </c>
       <c r="I64" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J64" t="e">
         <v>#N/A</v>
@@ -7202,7 +7195,7 @@
       <c r="B65" t="s">
         <v>241</v>
       </c>
-      <c r="C65" s="29" t="s">
+      <c r="C65" t="s">
         <v>242</v>
       </c>
       <c r="D65" t="s">
@@ -7221,7 +7214,7 @@
         <v>1.08869</v>
       </c>
       <c r="I65" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J65" t="e">
         <v>#N/A</v>
@@ -7279,7 +7272,7 @@
       <c r="B66" t="s">
         <v>241</v>
       </c>
-      <c r="C66" s="29" t="s">
+      <c r="C66" t="s">
         <v>242</v>
       </c>
       <c r="D66" t="s">
@@ -7298,7 +7291,7 @@
         <v>1.09003</v>
       </c>
       <c r="I66" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J66" t="e">
         <v>#N/A</v>
@@ -7356,7 +7349,7 @@
       <c r="B67" t="s">
         <v>241</v>
       </c>
-      <c r="C67" s="29" t="s">
+      <c r="C67" t="s">
         <v>242</v>
       </c>
       <c r="D67" t="s">
@@ -7375,7 +7368,7 @@
         <v>1.09267</v>
       </c>
       <c r="I67" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J67" t="e">
         <v>#N/A</v>
@@ -7433,7 +7426,7 @@
       <c r="B68" t="s">
         <v>241</v>
       </c>
-      <c r="C68" s="29" t="s">
+      <c r="C68" t="s">
         <v>242</v>
       </c>
       <c r="D68" t="s">
@@ -7452,7 +7445,7 @@
         <v>1.09471</v>
       </c>
       <c r="I68" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J68" t="e">
         <v>#N/A</v>
@@ -7510,7 +7503,7 @@
       <c r="B69" t="s">
         <v>241</v>
       </c>
-      <c r="C69" s="29" t="s">
+      <c r="C69" t="s">
         <v>242</v>
       </c>
       <c r="D69" t="s">
@@ -7529,7 +7522,7 @@
         <v>1.09946</v>
       </c>
       <c r="I69" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J69" t="e">
         <v>#N/A</v>
@@ -7587,7 +7580,7 @@
       <c r="B70" t="s">
         <v>241</v>
       </c>
-      <c r="C70" s="29" t="s">
+      <c r="C70" t="s">
         <v>242</v>
       </c>
       <c r="D70" t="s">
@@ -7606,7 +7599,7 @@
         <v>1.10242</v>
       </c>
       <c r="I70" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J70" t="e">
         <v>#N/A</v>
@@ -7664,7 +7657,7 @@
       <c r="B71" t="s">
         <v>241</v>
       </c>
-      <c r="C71" s="29" t="s">
+      <c r="C71" t="s">
         <v>242</v>
       </c>
       <c r="D71" t="s">
@@ -7683,7 +7676,7 @@
         <v>1.10316</v>
       </c>
       <c r="I71" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J71" t="e">
         <v>#N/A</v>
@@ -7741,7 +7734,7 @@
       <c r="B72" t="s">
         <v>241</v>
       </c>
-      <c r="C72" s="29" t="s">
+      <c r="C72" t="s">
         <v>242</v>
       </c>
       <c r="D72" t="s">
@@ -7760,7 +7753,7 @@
         <v>1.1062</v>
       </c>
       <c r="I72" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J72" t="e">
         <v>#N/A</v>
@@ -7818,7 +7811,7 @@
       <c r="B73" t="s">
         <v>241</v>
       </c>
-      <c r="C73" s="29" t="s">
+      <c r="C73" t="s">
         <v>242</v>
       </c>
       <c r="D73" t="s">
@@ -7837,7 +7830,7 @@
         <v>1.10782</v>
       </c>
       <c r="I73" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J73" t="e">
         <v>#N/A</v>
@@ -7895,7 +7888,7 @@
       <c r="B74" t="s">
         <v>241</v>
       </c>
-      <c r="C74" s="29" t="s">
+      <c r="C74" t="s">
         <v>242</v>
       </c>
       <c r="D74" t="s">
@@ -7914,7 +7907,7 @@
         <v>1.1103</v>
       </c>
       <c r="I74" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J74" t="e">
         <v>#N/A</v>
@@ -7972,7 +7965,7 @@
       <c r="B75" t="s">
         <v>241</v>
       </c>
-      <c r="C75" s="29" t="s">
+      <c r="C75" t="s">
         <v>242</v>
       </c>
       <c r="D75" t="s">
@@ -7991,7 +7984,7 @@
         <v>1.1128</v>
       </c>
       <c r="I75" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J75" t="e">
         <v>#N/A</v>
@@ -8049,7 +8042,7 @@
       <c r="B76" t="s">
         <v>241</v>
       </c>
-      <c r="C76" s="29" t="s">
+      <c r="C76" t="s">
         <v>242</v>
       </c>
       <c r="D76" t="s">
@@ -8068,7 +8061,7 @@
         <v>1.11526</v>
       </c>
       <c r="I76" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J76" t="e">
         <v>#N/A</v>
@@ -8126,7 +8119,7 @@
       <c r="B77" t="s">
         <v>241</v>
       </c>
-      <c r="C77" s="29" t="s">
+      <c r="C77" t="s">
         <v>242</v>
       </c>
       <c r="D77" t="s">
@@ -8145,7 +8138,7 @@
         <v>1.11786</v>
       </c>
       <c r="I77" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J77" t="e">
         <v>#N/A</v>
@@ -8203,7 +8196,7 @@
       <c r="B78" t="s">
         <v>241</v>
       </c>
-      <c r="C78" s="29" t="s">
+      <c r="C78" t="s">
         <v>242</v>
       </c>
       <c r="D78" t="s">
@@ -8222,7 +8215,7 @@
         <v>1.12036</v>
       </c>
       <c r="I78" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J78" t="e">
         <v>#N/A</v>
@@ -8280,7 +8273,7 @@
       <c r="B79" t="s">
         <v>241</v>
       </c>
-      <c r="C79" s="29" t="s">
+      <c r="C79" t="s">
         <v>242</v>
       </c>
       <c r="D79" t="s">
@@ -8299,7 +8292,7 @@
         <v>1.12309</v>
       </c>
       <c r="I79" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J79" t="e">
         <v>#N/A</v>
@@ -8357,7 +8350,7 @@
       <c r="B80" t="s">
         <v>241</v>
       </c>
-      <c r="C80" s="29" t="s">
+      <c r="C80" t="s">
         <v>242</v>
       </c>
       <c r="D80" t="s">
@@ -8376,7 +8369,7 @@
         <v>1.12606</v>
       </c>
       <c r="I80" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J80" t="e">
         <v>#N/A</v>
@@ -8434,7 +8427,7 @@
       <c r="B81" t="s">
         <v>241</v>
       </c>
-      <c r="C81" s="29" t="s">
+      <c r="C81" t="s">
         <v>242</v>
       </c>
       <c r="D81" t="s">
@@ -8453,7 +8446,7 @@
         <v>1.12781</v>
       </c>
       <c r="I81" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J81" t="e">
         <v>#N/A</v>
@@ -8511,7 +8504,7 @@
       <c r="B82" t="s">
         <v>241</v>
       </c>
-      <c r="C82" s="29" t="s">
+      <c r="C82" t="s">
         <v>242</v>
       </c>
       <c r="D82" t="s">
@@ -8530,7 +8523,7 @@
         <v>1.13097</v>
       </c>
       <c r="I82" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J82" t="e">
         <v>#N/A</v>
@@ -8588,7 +8581,7 @@
       <c r="B83" t="s">
         <v>241</v>
       </c>
-      <c r="C83" s="29" t="s">
+      <c r="C83" t="s">
         <v>242</v>
       </c>
       <c r="D83" t="s">
@@ -8607,7 +8600,7 @@
         <v>1.13657</v>
       </c>
       <c r="I83" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J83" t="e">
         <v>#N/A</v>
@@ -8665,7 +8658,7 @@
       <c r="B84" t="s">
         <v>241</v>
       </c>
-      <c r="C84" s="29" t="s">
+      <c r="C84" t="s">
         <v>242</v>
       </c>
       <c r="D84" t="s">
@@ -8684,7 +8677,7 @@
         <v>1.14003</v>
       </c>
       <c r="I84" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J84" t="e">
         <v>#N/A</v>
@@ -8742,7 +8735,7 @@
       <c r="B85" t="s">
         <v>241</v>
       </c>
-      <c r="C85" s="29" t="s">
+      <c r="C85" t="s">
         <v>242</v>
       </c>
       <c r="D85" t="s">
@@ -8761,7 +8754,7 @@
         <v>1.14323</v>
       </c>
       <c r="I85" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J85" t="e">
         <v>#N/A</v>
@@ -8819,7 +8812,7 @@
       <c r="B86" t="s">
         <v>241</v>
       </c>
-      <c r="C86" s="29" t="s">
+      <c r="C86" t="s">
         <v>242</v>
       </c>
       <c r="D86" t="s">
@@ -8838,7 +8831,7 @@
         <v>1.14533</v>
       </c>
       <c r="I86" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J86" t="e">
         <v>#N/A</v>
@@ -8896,7 +8889,7 @@
       <c r="B87" t="s">
         <v>241</v>
       </c>
-      <c r="C87" s="29" t="s">
+      <c r="C87" t="s">
         <v>242</v>
       </c>
       <c r="D87" t="s">
@@ -8915,7 +8908,7 @@
         <v>1.1489</v>
       </c>
       <c r="I87" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J87" t="e">
         <v>#N/A</v>
@@ -8973,7 +8966,7 @@
       <c r="B88" t="s">
         <v>241</v>
       </c>
-      <c r="C88" s="29" t="s">
+      <c r="C88" t="s">
         <v>242</v>
       </c>
       <c r="D88" t="s">
@@ -8992,7 +8985,7 @@
         <v>1.15094</v>
       </c>
       <c r="I88" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J88" t="e">
         <v>#N/A</v>
@@ -9050,7 +9043,7 @@
       <c r="B89" t="s">
         <v>241</v>
       </c>
-      <c r="C89" s="29" t="s">
+      <c r="C89" t="s">
         <v>242</v>
       </c>
       <c r="D89" t="s">
@@ -9069,7 +9062,7 @@
         <v>1.15409</v>
       </c>
       <c r="I89" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J89" t="e">
         <v>#N/A</v>
@@ -9127,7 +9120,7 @@
       <c r="B90" t="s">
         <v>241</v>
       </c>
-      <c r="C90" s="29" t="s">
+      <c r="C90" t="s">
         <v>242</v>
       </c>
       <c r="D90" t="s">
@@ -9146,7 +9139,7 @@
         <v>1.15777</v>
       </c>
       <c r="I90" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J90" t="e">
         <v>#N/A</v>
@@ -9204,7 +9197,7 @@
       <c r="B91" t="s">
         <v>241</v>
       </c>
-      <c r="C91" s="29" t="s">
+      <c r="C91" t="s">
         <v>242</v>
       </c>
       <c r="D91" t="s">
@@ -9223,7 +9216,7 @@
         <v>1.16073</v>
       </c>
       <c r="I91" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J91" t="e">
         <v>#N/A</v>
@@ -9281,7 +9274,7 @@
       <c r="B92" t="s">
         <v>241</v>
       </c>
-      <c r="C92" s="29" t="s">
+      <c r="C92" t="s">
         <v>242</v>
       </c>
       <c r="D92" t="s">
@@ -9300,7 +9293,7 @@
         <v>1.16285</v>
       </c>
       <c r="I92" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J92" t="e">
         <v>#N/A</v>
@@ -9358,7 +9351,7 @@
       <c r="B93" t="s">
         <v>241</v>
       </c>
-      <c r="C93" s="29" t="s">
+      <c r="C93" t="s">
         <v>242</v>
       </c>
       <c r="D93" t="s">
@@ -9377,7 +9370,7 @@
         <v>1.16986</v>
       </c>
       <c r="I93" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J93" t="e">
         <v>#N/A</v>
@@ -9435,7 +9428,7 @@
       <c r="B94" t="s">
         <v>241</v>
       </c>
-      <c r="C94" s="29" t="s">
+      <c r="C94" t="s">
         <v>242</v>
       </c>
       <c r="D94" t="s">
@@ -9454,7 +9447,7 @@
         <v>1.17757</v>
       </c>
       <c r="I94" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J94" t="e">
         <v>#N/A</v>
@@ -9512,7 +9505,7 @@
       <c r="B95" t="s">
         <v>241</v>
       </c>
-      <c r="C95" s="29" t="s">
+      <c r="C95" t="s">
         <v>242</v>
       </c>
       <c r="D95" t="s">
@@ -9531,7 +9524,7 @@
         <v>1.17966</v>
       </c>
       <c r="I95" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J95" t="e">
         <v>#N/A</v>
@@ -9589,7 +9582,7 @@
       <c r="B96" t="s">
         <v>241</v>
       </c>
-      <c r="C96" s="29" t="s">
+      <c r="C96" t="s">
         <v>242</v>
       </c>
       <c r="D96" t="s">
@@ -9608,7 +9601,7 @@
         <v>1.18175</v>
       </c>
       <c r="I96" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J96" t="e">
         <v>#N/A</v>
@@ -9666,7 +9659,7 @@
       <c r="B97" t="s">
         <v>241</v>
       </c>
-      <c r="C97" s="29" t="s">
+      <c r="C97" t="s">
         <v>242</v>
       </c>
       <c r="D97" t="s">
@@ -9685,7 +9678,7 @@
         <v>1.18406</v>
       </c>
       <c r="I97" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J97" t="e">
         <v>#N/A</v>
@@ -9743,7 +9736,7 @@
       <c r="B98" t="s">
         <v>241</v>
       </c>
-      <c r="C98" s="29" t="s">
+      <c r="C98" t="s">
         <v>242</v>
       </c>
       <c r="D98" t="s">
@@ -9762,7 +9755,7 @@
         <v>1.18597</v>
       </c>
       <c r="I98" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J98" t="e">
         <v>#N/A</v>
@@ -9820,7 +9813,7 @@
       <c r="B99" t="s">
         <v>241</v>
       </c>
-      <c r="C99" s="29" t="s">
+      <c r="C99" t="s">
         <v>242</v>
       </c>
       <c r="D99" t="s">
@@ -9839,7 +9832,7 @@
         <v>1.18807</v>
       </c>
       <c r="I99" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J99" t="e">
         <v>#N/A</v>
@@ -9897,7 +9890,7 @@
       <c r="B100" t="s">
         <v>241</v>
       </c>
-      <c r="C100" s="29" t="s">
+      <c r="C100" t="s">
         <v>242</v>
       </c>
       <c r="D100" t="s">
@@ -9916,7 +9909,7 @@
         <v>1.19131</v>
       </c>
       <c r="I100" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J100" t="e">
         <v>#N/A</v>
@@ -9974,7 +9967,7 @@
       <c r="B101" t="s">
         <v>241</v>
       </c>
-      <c r="C101" s="29" t="s">
+      <c r="C101" t="s">
         <v>242</v>
       </c>
       <c r="D101" t="s">
@@ -9993,7 +9986,7 @@
         <v>1.19515</v>
       </c>
       <c r="I101" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J101" t="e">
         <v>#N/A</v>
@@ -10051,7 +10044,7 @@
       <c r="B102" t="s">
         <v>241</v>
       </c>
-      <c r="C102" s="29" t="s">
+      <c r="C102" t="s">
         <v>242</v>
       </c>
       <c r="D102" t="s">
@@ -10070,7 +10063,7 @@
         <v>1.20326</v>
       </c>
       <c r="I102" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J102" t="e">
         <v>#N/A</v>
@@ -10128,7 +10121,7 @@
       <c r="B103" t="s">
         <v>241</v>
       </c>
-      <c r="C103" s="29" t="s">
+      <c r="C103" t="s">
         <v>242</v>
       </c>
       <c r="D103" t="s">
@@ -10147,7 +10140,7 @@
         <v>1.20676</v>
       </c>
       <c r="I103" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J103" t="e">
         <v>#N/A</v>
@@ -10205,7 +10198,7 @@
       <c r="B104" t="s">
         <v>241</v>
       </c>
-      <c r="C104" s="29" t="s">
+      <c r="C104" t="s">
         <v>242</v>
       </c>
       <c r="D104" t="s">
@@ -10224,7 +10217,7 @@
         <v>1.20999</v>
       </c>
       <c r="I104" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J104" t="e">
         <v>#N/A</v>
@@ -10282,7 +10275,7 @@
       <c r="B105" t="s">
         <v>241</v>
       </c>
-      <c r="C105" s="29" t="s">
+      <c r="C105" t="s">
         <v>242</v>
       </c>
       <c r="D105" t="s">
@@ -10301,7 +10294,7 @@
         <v>1.21448</v>
       </c>
       <c r="I105" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J105" t="e">
         <v>#N/A</v>
@@ -10359,7 +10352,7 @@
       <c r="B106" t="s">
         <v>241</v>
       </c>
-      <c r="C106" s="29" t="s">
+      <c r="C106" t="s">
         <v>242</v>
       </c>
       <c r="D106" t="s">
@@ -10378,7 +10371,7 @@
         <v>1.21642</v>
       </c>
       <c r="I106" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J106" t="e">
         <v>#N/A</v>
@@ -10436,7 +10429,7 @@
       <c r="B107" t="s">
         <v>241</v>
       </c>
-      <c r="C107" s="29" t="s">
+      <c r="C107" t="s">
         <v>242</v>
       </c>
       <c r="D107" t="s">
@@ -10455,7 +10448,7 @@
         <v>1.21854</v>
       </c>
       <c r="I107" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J107" t="e">
         <v>#N/A</v>
@@ -10513,7 +10506,7 @@
       <c r="B108" t="s">
         <v>241</v>
       </c>
-      <c r="C108" s="29" t="s">
+      <c r="C108" t="s">
         <v>242</v>
       </c>
       <c r="D108" t="s">
@@ -10532,7 +10525,7 @@
         <v>1.22418</v>
       </c>
       <c r="I108" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J108" t="e">
         <v>#N/A</v>
@@ -10590,7 +10583,7 @@
       <c r="B109" t="s">
         <v>241</v>
       </c>
-      <c r="C109" s="29" t="s">
+      <c r="C109" t="s">
         <v>242</v>
       </c>
       <c r="D109" t="s">
@@ -10609,7 +10602,7 @@
         <v>1.22717</v>
       </c>
       <c r="I109" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J109" t="e">
         <v>#N/A</v>
@@ -10667,7 +10660,7 @@
       <c r="B110" t="s">
         <v>241</v>
       </c>
-      <c r="C110" s="29" t="s">
+      <c r="C110" t="s">
         <v>242</v>
       </c>
       <c r="D110" t="s">
@@ -10686,7 +10679,7 @@
         <v>1.23072</v>
       </c>
       <c r="I110" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J110" t="e">
         <v>#N/A</v>
@@ -10744,7 +10737,7 @@
       <c r="B111" t="s">
         <v>241</v>
       </c>
-      <c r="C111" s="29" t="s">
+      <c r="C111" t="s">
         <v>242</v>
       </c>
       <c r="D111" t="s">
@@ -10763,7 +10756,7 @@
         <v>1.2339</v>
       </c>
       <c r="I111" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J111" t="e">
         <v>#N/A</v>
@@ -10821,7 +10814,7 @@
       <c r="B112" t="s">
         <v>241</v>
       </c>
-      <c r="C112" s="29" t="s">
+      <c r="C112" t="s">
         <v>242</v>
       </c>
       <c r="D112" t="s">
@@ -10840,7 +10833,7 @@
         <v>1.23618</v>
       </c>
       <c r="I112" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J112" t="e">
         <v>#N/A</v>
@@ -10898,7 +10891,7 @@
       <c r="B113" t="s">
         <v>241</v>
       </c>
-      <c r="C113" s="29" t="s">
+      <c r="C113" t="s">
         <v>242</v>
       </c>
       <c r="D113" t="s">
@@ -10917,7 +10910,7 @@
         <v>1.23983</v>
       </c>
       <c r="I113" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J113" t="e">
         <v>#N/A</v>
@@ -10975,7 +10968,7 @@
       <c r="B114" t="s">
         <v>241</v>
       </c>
-      <c r="C114" s="29" t="s">
+      <c r="C114" t="s">
         <v>242</v>
       </c>
       <c r="D114" t="s">
@@ -10994,7 +10987,7 @@
         <v>1.24325</v>
       </c>
       <c r="I114" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="J114" t="e">
         <v>#N/A</v>
@@ -11051,118 +11044,6 @@
       <formula>#REF!="no"</formula>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1h"/>
-    <hyperlink ref="C6" r:id="rId2h"/>
-    <hyperlink ref="C7" r:id="rId3h"/>
-    <hyperlink ref="C8" r:id="rId4h"/>
-    <hyperlink ref="C9" r:id="rId5h"/>
-    <hyperlink ref="C10" r:id="rId6h"/>
-    <hyperlink ref="C11" r:id="rId7h"/>
-    <hyperlink ref="C12" r:id="rId8h"/>
-    <hyperlink ref="C13" r:id="rId9h"/>
-    <hyperlink ref="C14" r:id="rId10h"/>
-    <hyperlink ref="C15" r:id="rId11h"/>
-    <hyperlink ref="C16" r:id="rId12h"/>
-    <hyperlink ref="C17" r:id="rId13h"/>
-    <hyperlink ref="C18" r:id="rId14h"/>
-    <hyperlink ref="C19" r:id="rId15h"/>
-    <hyperlink ref="C20" r:id="rId16h"/>
-    <hyperlink ref="C21" r:id="rId17h"/>
-    <hyperlink ref="C22" r:id="rId18h"/>
-    <hyperlink ref="C23" r:id="rId19h"/>
-    <hyperlink ref="C24" r:id="rId20h"/>
-    <hyperlink ref="C25" r:id="rId21h"/>
-    <hyperlink ref="C26" r:id="rId22h"/>
-    <hyperlink ref="C27" r:id="rId23h"/>
-    <hyperlink ref="C28" r:id="rId24h"/>
-    <hyperlink ref="C29" r:id="rId25h"/>
-    <hyperlink ref="C30" r:id="rId26h"/>
-    <hyperlink ref="C31" r:id="rId27h"/>
-    <hyperlink ref="C32" r:id="rId28h"/>
-    <hyperlink ref="C33" r:id="rId29h"/>
-    <hyperlink ref="C34" r:id="rId30h"/>
-    <hyperlink ref="C35" r:id="rId31h"/>
-    <hyperlink ref="C36" r:id="rId32h"/>
-    <hyperlink ref="C37" r:id="rId33h"/>
-    <hyperlink ref="C38" r:id="rId34h"/>
-    <hyperlink ref="C39" r:id="rId35h"/>
-    <hyperlink ref="C40" r:id="rId36h"/>
-    <hyperlink ref="C41" r:id="rId37h"/>
-    <hyperlink ref="C42" r:id="rId38h"/>
-    <hyperlink ref="C43" r:id="rId39h"/>
-    <hyperlink ref="C44" r:id="rId40h"/>
-    <hyperlink ref="C45" r:id="rId41h"/>
-    <hyperlink ref="C46" r:id="rId42h"/>
-    <hyperlink ref="C47" r:id="rId43h"/>
-    <hyperlink ref="C48" r:id="rId44h"/>
-    <hyperlink ref="C49" r:id="rId45h"/>
-    <hyperlink ref="C50" r:id="rId46h"/>
-    <hyperlink ref="C51" r:id="rId47h"/>
-    <hyperlink ref="C52" r:id="rId48h"/>
-    <hyperlink ref="C53" r:id="rId49h"/>
-    <hyperlink ref="C54" r:id="rId50h"/>
-    <hyperlink ref="C55" r:id="rId51h"/>
-    <hyperlink ref="C56" r:id="rId52h"/>
-    <hyperlink ref="C57" r:id="rId53h"/>
-    <hyperlink ref="C58" r:id="rId54h"/>
-    <hyperlink ref="C59" r:id="rId55h"/>
-    <hyperlink ref="C60" r:id="rId56h"/>
-    <hyperlink ref="C61" r:id="rId57h"/>
-    <hyperlink ref="C62" r:id="rId58h"/>
-    <hyperlink ref="C63" r:id="rId59h"/>
-    <hyperlink ref="C64" r:id="rId60h"/>
-    <hyperlink ref="C65" r:id="rId61h"/>
-    <hyperlink ref="C66" r:id="rId62h"/>
-    <hyperlink ref="C67" r:id="rId63h"/>
-    <hyperlink ref="C68" r:id="rId64h"/>
-    <hyperlink ref="C69" r:id="rId65h"/>
-    <hyperlink ref="C70" r:id="rId66h"/>
-    <hyperlink ref="C71" r:id="rId67h"/>
-    <hyperlink ref="C72" r:id="rId68h"/>
-    <hyperlink ref="C73" r:id="rId69h"/>
-    <hyperlink ref="C74" r:id="rId70h"/>
-    <hyperlink ref="C75" r:id="rId71h"/>
-    <hyperlink ref="C76" r:id="rId72h"/>
-    <hyperlink ref="C77" r:id="rId73h"/>
-    <hyperlink ref="C78" r:id="rId74h"/>
-    <hyperlink ref="C79" r:id="rId75h"/>
-    <hyperlink ref="C80" r:id="rId76h"/>
-    <hyperlink ref="C81" r:id="rId77h"/>
-    <hyperlink ref="C82" r:id="rId78h"/>
-    <hyperlink ref="C83" r:id="rId79h"/>
-    <hyperlink ref="C84" r:id="rId80h"/>
-    <hyperlink ref="C85" r:id="rId81h"/>
-    <hyperlink ref="C86" r:id="rId82h"/>
-    <hyperlink ref="C87" r:id="rId83h"/>
-    <hyperlink ref="C88" r:id="rId84h"/>
-    <hyperlink ref="C89" r:id="rId85h"/>
-    <hyperlink ref="C90" r:id="rId86h"/>
-    <hyperlink ref="C91" r:id="rId87h"/>
-    <hyperlink ref="C92" r:id="rId88h"/>
-    <hyperlink ref="C93" r:id="rId89h"/>
-    <hyperlink ref="C94" r:id="rId90h"/>
-    <hyperlink ref="C95" r:id="rId91h"/>
-    <hyperlink ref="C96" r:id="rId92h"/>
-    <hyperlink ref="C97" r:id="rId93h"/>
-    <hyperlink ref="C98" r:id="rId94h"/>
-    <hyperlink ref="C99" r:id="rId95h"/>
-    <hyperlink ref="C100" r:id="rId96h"/>
-    <hyperlink ref="C101" r:id="rId97h"/>
-    <hyperlink ref="C102" r:id="rId98h"/>
-    <hyperlink ref="C103" r:id="rId99h"/>
-    <hyperlink ref="C104" r:id="rId100h"/>
-    <hyperlink ref="C105" r:id="rId101h"/>
-    <hyperlink ref="C106" r:id="rId102h"/>
-    <hyperlink ref="C107" r:id="rId103h"/>
-    <hyperlink ref="C108" r:id="rId104h"/>
-    <hyperlink ref="C109" r:id="rId105h"/>
-    <hyperlink ref="C110" r:id="rId106h"/>
-    <hyperlink ref="C111" r:id="rId107h"/>
-    <hyperlink ref="C112" r:id="rId108h"/>
-    <hyperlink ref="C113" r:id="rId109h"/>
-    <hyperlink ref="C114" r:id="rId110h"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
